--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_15.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/2000000/Output_0_15.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>716371.8036446588</v>
+        <v>716379.1415249447</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>925658.2446351536</v>
+        <v>925399.3994514378</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18327269.62422523</v>
+        <v>18327015.93006067</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5283567.215382143</v>
+        <v>5283674.776931894</v>
       </c>
     </row>
     <row r="11">
@@ -697,25 +697,25 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>202.2946864288972</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X2" t="n">
-        <v>11.16618163507844</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y2" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="3">
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>146.1378473354543</v>
+        <v>146.1932996118735</v>
       </c>
       <c r="D3" t="n">
         <v>147.4450655646388</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -852,7 +852,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R4" t="n">
-        <v>47.02492433367362</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -892,22 +892,22 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G5" t="n">
-        <v>230.8476210749815</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H5" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I5" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J5" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -965,28 +965,28 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>145.4467082856156</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -1010,22 +1010,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>4.525096818297269</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1086,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>24.75543250779077</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1129,19 +1129,19 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>210.4758895704059</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1168,19 +1168,19 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>112.3289263072337</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1256,10 +1256,10 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U9" t="n">
-        <v>225.9413820809748</v>
+        <v>28.88985408777983</v>
       </c>
       <c r="V9" t="n">
-        <v>89.13402707682593</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1293,19 +1293,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>93.35918011667277</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1366,16 +1366,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>210.4758895704059</v>
@@ -1408,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>19.72793538656374</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1484,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>171.6831711038378</v>
+        <v>85.31372784089217</v>
       </c>
       <c r="T12" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.525096818297269</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="13">
@@ -1536,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>17.55829564281238</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K13" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1560,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>39.82778746869526</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1603,16 +1603,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>1.809496073036132</v>
       </c>
       <c r="F14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H14" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I14" t="n">
         <v>210.4758895704059</v>
@@ -1639,7 +1639,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.79691042959408</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -1676,25 +1676,25 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0.7465913262578567</v>
@@ -1724,19 +1724,19 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>110.0262741840913</v>
+        <v>34.66067414728066</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>17.55829564281238</v>
+        <v>17.55829564281241</v>
       </c>
       <c r="J16" t="n">
         <v>93.35918011667277</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H17" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I17" t="n">
-        <v>202.2821007854552</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>78.98946446248301</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1934,7 +1934,7 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1976,10 +1976,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>85.25827556447292</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2037,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2125,19 +2125,19 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
     </row>
     <row r="21">
@@ -2147,10 +2147,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>141.2503478936304</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
         <v>147.4450655646388</v>
@@ -2159,10 +2159,10 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>84.56713651463426</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2213,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="22">
@@ -2247,52 +2247,52 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>200.3360962888297</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -2314,13 +2314,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>202.282100785513</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2371,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -2387,13 +2387,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>109.4031921034048</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2441,13 +2441,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>50.01653186979276</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X24" t="n">
         <v>205.7729852034775</v>
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -2551,10 +2551,10 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -2590,19 +2590,19 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>80.30783249471884</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -2611,7 +2611,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
     </row>
     <row r="27">
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>98.47382483861915</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -2672,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2684,13 +2684,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>29.01125423986453</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="28">
@@ -2779,7 +2779,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -2788,22 +2788,22 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>200.3360962888296</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>230.176950435912</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="30">
@@ -2861,7 +2861,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>123.7367568936677</v>
+        <v>123.7922091700869</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -2940,73 +2940,73 @@
         <v>0</v>
       </c>
       <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3016,22 +3016,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -3040,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>5.877922149011282e-11</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -3070,16 +3070,16 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>212.2728000000722</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>29.01125423986453</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -3146,25 +3146,25 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X33" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>144.1493081031292</v>
       </c>
     </row>
     <row r="34">
@@ -3225,19 +3225,19 @@
         <v>0</v>
       </c>
       <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -3253,10 +3253,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C35" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -3265,10 +3265,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>5.877922149011282e-11</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -3316,13 +3316,13 @@
         <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y35" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -3335,16 +3335,16 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>66.53813710775646</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,19 +3383,19 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>200.1647286948216</v>
+        <v>156.0235939482764</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3426,40 +3426,40 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3493,28 +3493,28 @@
         <v>0</v>
       </c>
       <c r="C38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>241</v>
+        <v>58.39471844666277</v>
       </c>
       <c r="G38" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3538,13 +3538,13 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3569,25 +3569,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>134.6300547079683</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -3626,19 +3626,19 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>49.3111039422953</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -3702,10 +3702,10 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
       </c>
       <c r="V40" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>52.42556848774763</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
@@ -3739,7 +3739,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -3772,22 +3772,22 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
         <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>112.2877629084735</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V41" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="42">
@@ -3806,22 +3806,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -3857,25 +3857,25 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>7.837102735344149</v>
       </c>
       <c r="T42" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>34.61951074852038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3951,7 +3951,7 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>47.02492433367365</v>
       </c>
       <c r="Y43" t="n">
         <v>0</v>
@@ -3970,22 +3970,22 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>52.41298284430552</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4009,22 +4009,22 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>212.285385643442</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
@@ -4033,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4043,31 +4043,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1.197928092376224</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>110.0316218122009</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -4091,13 +4091,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="46">
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -4289,76 +4289,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K2" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L2" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M2" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N2" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O2" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P2" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q2" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R2" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="S2" t="n">
-        <v>742.7770012113231</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="T2" t="n">
-        <v>517.427658217251</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="U2" t="n">
-        <v>273.9933147829075</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="V2" t="n">
-        <v>273.9933147829075</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W2" t="n">
-        <v>273.9933147829075</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="X2" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y2" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="3">
@@ -4368,76 +4368,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C3" t="n">
-        <v>816.3860127924704</v>
+        <v>816.3871559026832</v>
       </c>
       <c r="D3" t="n">
-        <v>667.4516031312191</v>
+        <v>667.4527462414319</v>
       </c>
       <c r="E3" t="n">
-        <v>508.2141481257637</v>
+        <v>508.2152912359765</v>
       </c>
       <c r="F3" t="n">
-        <v>361.6795901526487</v>
+        <v>361.6807332628614</v>
       </c>
       <c r="G3" t="n">
-        <v>222.9487647352642</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H3" t="n">
-        <v>109.5796291428435</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J3" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K3" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L3" t="n">
-        <v>234.7819638733197</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M3" t="n">
-        <v>473.3719638733197</v>
+        <v>383.2428491569326</v>
       </c>
       <c r="N3" t="n">
-        <v>711.9619638733197</v>
+        <v>621.8469951458151</v>
       </c>
       <c r="O3" t="n">
-        <v>711.9619638733197</v>
+        <v>860.4511411346975</v>
       </c>
       <c r="P3" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y3" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="4">
@@ -4447,76 +4447,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="C4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="D4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="E4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="F4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="G4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="H4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K4" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L4" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M4" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N4" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P4" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q4" t="n">
-        <v>66.7799235693673</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="T4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="U4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="V4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="W4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="X4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="Y4" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
     </row>
     <row r="5">
@@ -4526,76 +4526,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C5" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D5" t="n">
-        <v>720.5656565656566</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E5" t="n">
-        <v>720.5656565656566</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="F5" t="n">
-        <v>720.5656565656566</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G5" t="n">
-        <v>487.3862413384025</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H5" t="n">
-        <v>243.9518979040591</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I5" t="n">
-        <v>31.34998924708335</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J5" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K5" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L5" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M5" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N5" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O5" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y5" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="6">
@@ -4605,76 +4605,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C6" t="n">
-        <v>19.28</v>
+        <v>817.1412885554689</v>
       </c>
       <c r="D6" t="n">
-        <v>19.28</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E6" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F6" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G6" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H6" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I6" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K6" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L6" t="n">
-        <v>249.2431058683491</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M6" t="n">
-        <v>473.3719638733197</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N6" t="n">
-        <v>473.3719638733197</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O6" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P6" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q6" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R6" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S6" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T6" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U6" t="n">
-        <v>259.0029130987097</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V6" t="n">
-        <v>23.85080486696694</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y6" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="7">
@@ -4684,76 +4684,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J7" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K7" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L7" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M7" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N7" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P7" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q7" t="n">
-        <v>66.7799235693673</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y7" t="n">
-        <v>41.77443618776046</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="8">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E8" t="n">
-        <v>962.184938960006</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F8" t="n">
-        <v>718.7505955256626</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G8" t="n">
-        <v>475.3162520913191</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H8" t="n">
-        <v>231.8819086569757</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J8" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K8" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L8" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M8" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N8" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O8" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R8" t="n">
-        <v>964</v>
+        <v>812.6742080953335</v>
       </c>
       <c r="S8" t="n">
-        <v>964</v>
+        <v>601.5428246748836</v>
       </c>
       <c r="T8" t="n">
-        <v>964</v>
+        <v>376.1934816808115</v>
       </c>
       <c r="U8" t="n">
-        <v>964</v>
+        <v>132.7447050367114</v>
       </c>
       <c r="V8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y8" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="C9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="D9" t="n">
-        <v>20.03413265278571</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="E9" t="n">
-        <v>20.03413265278571</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="F9" t="n">
-        <v>20.03413265278571</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="G9" t="n">
-        <v>20.03413265278571</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="H9" t="n">
-        <v>20.03413265278571</v>
+        <v>109.5807722530562</v>
       </c>
       <c r="I9" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J9" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K9" t="n">
-        <v>19.28</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L9" t="n">
-        <v>249.2431058683491</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M9" t="n">
-        <v>487.8331058683492</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N9" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O9" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P9" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R9" t="n">
-        <v>862.8304705528857</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S9" t="n">
-        <v>689.4131260035546</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T9" t="n">
-        <v>487.2265313623206</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U9" t="n">
-        <v>259.0029130987097</v>
+        <v>458.1020160772196</v>
       </c>
       <c r="V9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="W9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="X9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
       <c r="Y9" t="n">
-        <v>168.968542314037</v>
+        <v>222.9499078454769</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H10" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I10" t="n">
-        <v>136.0766383258138</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J10" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K10" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L10" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M10" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N10" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y10" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="C11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="D11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="E11" t="n">
-        <v>962.184938960006</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="F11" t="n">
-        <v>718.7505955256626</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="G11" t="n">
-        <v>475.3162520913191</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="H11" t="n">
-        <v>231.8819086569757</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J11" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K11" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L11" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M11" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N11" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O11" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R11" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S11" t="n">
-        <v>964</v>
+        <v>944.1299480494607</v>
       </c>
       <c r="T11" t="n">
-        <v>964</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="U11" t="n">
-        <v>964</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="V11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="W11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="X11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="Y11" t="n">
-        <v>964</v>
+        <v>231.8830517671884</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19.28</v>
+        <v>501.9060370580465</v>
       </c>
       <c r="C12" t="n">
-        <v>19.28</v>
+        <v>327.4530077769195</v>
       </c>
       <c r="D12" t="n">
-        <v>19.28</v>
+        <v>178.5185981156682</v>
       </c>
       <c r="E12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J12" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K12" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L12" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M12" t="n">
-        <v>613.1906659261865</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N12" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O12" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q12" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R12" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S12" t="n">
-        <v>689.4131260035546</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="T12" t="n">
-        <v>487.2265313623206</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="U12" t="n">
-        <v>259.0029130987097</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="V12" t="n">
-        <v>23.85080486696694</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="W12" t="n">
-        <v>19.28</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="X12" t="n">
-        <v>19.28</v>
+        <v>877.8816728430684</v>
       </c>
       <c r="Y12" t="n">
-        <v>19.28</v>
+        <v>670.1213740781145</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="C13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="D13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="E13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="F13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="G13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="H13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="I13" t="n">
-        <v>136.0766383258138</v>
+        <v>113.583345248266</v>
       </c>
       <c r="J13" t="n">
-        <v>41.77443618776046</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L13" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M13" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N13" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P13" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="R13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="S13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="T13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="U13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="V13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="W13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="X13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
       <c r="Y13" t="n">
-        <v>153.8122904902707</v>
+        <v>113.583345248266</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E14" t="n">
-        <v>962.184938960006</v>
+        <v>962.2293816994886</v>
       </c>
       <c r="F14" t="n">
-        <v>718.7505955256626</v>
+        <v>718.7806050553886</v>
       </c>
       <c r="G14" t="n">
-        <v>475.3162520913191</v>
+        <v>475.3318284112885</v>
       </c>
       <c r="H14" t="n">
-        <v>231.8819086569757</v>
+        <v>231.8830517671884</v>
       </c>
       <c r="I14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J14" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K14" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L14" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M14" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N14" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O14" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P14" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y14" t="n">
-        <v>962.184938960006</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>852.8623493089987</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C15" t="n">
-        <v>678.4093200278717</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D15" t="n">
-        <v>529.4749103666204</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E15" t="n">
-        <v>370.237455361165</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F15" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G15" t="n">
-        <v>223.7028973880499</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H15" t="n">
-        <v>110.3337617956292</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I15" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J15" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K15" t="n">
-        <v>144.6375600578374</v>
+        <v>65.60123993063803</v>
       </c>
       <c r="L15" t="n">
-        <v>374.6006659261865</v>
+        <v>65.60123993063803</v>
       </c>
       <c r="M15" t="n">
-        <v>542.7665223866492</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N15" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O15" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R15" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S15" t="n">
-        <v>852.8623493089987</v>
+        <v>929.0463735436861</v>
       </c>
       <c r="T15" t="n">
-        <v>852.8623493089987</v>
+        <v>726.8597789024521</v>
       </c>
       <c r="U15" t="n">
-        <v>852.8623493089987</v>
+        <v>498.6361606388412</v>
       </c>
       <c r="V15" t="n">
-        <v>852.8623493089987</v>
+        <v>263.4840524070985</v>
       </c>
       <c r="W15" t="n">
-        <v>852.8623493089987</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="X15" t="n">
-        <v>852.8623493089987</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="Y15" t="n">
-        <v>852.8623493089987</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="I16" t="n">
-        <v>136.0766383258138</v>
+        <v>136.0777814360265</v>
       </c>
       <c r="J16" t="n">
-        <v>41.77443618776046</v>
+        <v>41.77557929797318</v>
       </c>
       <c r="K16" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L16" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M16" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N16" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y16" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="C17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="D17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="E17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="F17" t="n">
-        <v>710.4740411974295</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="G17" t="n">
-        <v>467.0396977630861</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="H17" t="n">
-        <v>223.6053543287427</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="I17" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J17" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K17" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L17" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M17" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N17" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O17" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P17" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y17" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>501.9048939478338</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="C18" t="n">
-        <v>327.4518646667068</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="D18" t="n">
-        <v>178.5174550054555</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="E18" t="n">
-        <v>19.28</v>
+        <v>99.82261360389037</v>
       </c>
       <c r="F18" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G18" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H18" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I18" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J18" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K18" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L18" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M18" t="n">
-        <v>473.3719638733197</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N18" t="n">
-        <v>473.3719638733197</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O18" t="n">
-        <v>711.9619638733197</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P18" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q18" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R18" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S18" t="n">
-        <v>964</v>
+        <v>689.4702815141908</v>
       </c>
       <c r="T18" t="n">
-        <v>964</v>
+        <v>487.2836868729568</v>
       </c>
       <c r="U18" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="V18" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="W18" t="n">
-        <v>964</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="X18" t="n">
-        <v>877.8805297328556</v>
+        <v>259.0600686093459</v>
       </c>
       <c r="Y18" t="n">
-        <v>670.1202309679018</v>
+        <v>259.0600686093459</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L19" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M19" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N19" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R19" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="C20" t="n">
-        <v>19.28</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="D20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F20" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>19.28</v>
+        <v>749.627473042513</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>756.1484997944672</v>
+        <v>588.0815197256143</v>
       </c>
       <c r="C21" t="n">
-        <v>613.471380709992</v>
+        <v>413.6284904444873</v>
       </c>
       <c r="D21" t="n">
-        <v>464.5369710487408</v>
+        <v>264.694080783236</v>
       </c>
       <c r="E21" t="n">
-        <v>305.2995160432853</v>
+        <v>105.4566257777805</v>
       </c>
       <c r="F21" t="n">
-        <v>158.7649580701702</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L21" t="n">
-        <v>249.2431058683491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M21" t="n">
-        <v>487.8331058683492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N21" t="n">
-        <v>656.0154414866706</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O21" t="n">
-        <v>894.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P21" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X21" t="n">
-        <v>756.1484997944672</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y21" t="n">
-        <v>756.1484997944672</v>
+        <v>756.2968567456824</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W22" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y22" t="n">
-        <v>153.8122904902707</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>749.5830303030303</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="C23" t="n">
-        <v>749.5830303030303</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="D23" t="n">
-        <v>749.5830303030303</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="E23" t="n">
-        <v>506.1486868686869</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="F23" t="n">
-        <v>262.7143434343434</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935105573</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450952159</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.29047235812</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.1449945653594</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.3399447080075</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964.0000000000584</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>953.9083846318314</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>953.9083846318314</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S23" t="n">
-        <v>953.9083846318314</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T23" t="n">
-        <v>953.9083846318314</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U23" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V23" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W23" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y23" t="n">
-        <v>749.5830303030303</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>19.28</v>
+        <v>304.9965798960495</v>
       </c>
       <c r="C24" t="n">
-        <v>19.28</v>
+        <v>130.5435506149225</v>
       </c>
       <c r="D24" t="n">
-        <v>19.28</v>
+        <v>130.5435506149225</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L24" t="n">
-        <v>178.8354414866706</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M24" t="n">
-        <v>417.4254414866706</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N24" t="n">
-        <v>656.0154414866706</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>894.6054414866707</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U24" t="n">
-        <v>913.478250636573</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V24" t="n">
-        <v>678.3261424048302</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W24" t="n">
-        <v>434.8917989704868</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X24" t="n">
-        <v>227.0402987649539</v>
+        <v>512.7568786610034</v>
       </c>
       <c r="Y24" t="n">
-        <v>19.28</v>
+        <v>304.9965798960495</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E26" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S26" t="n">
-        <v>812.6170525846973</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T26" t="n">
-        <v>587.2677095906251</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U26" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V26" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="W26" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X26" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y26" t="n">
-        <v>506.1486868686869</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20.03413265278571</v>
+        <v>119.5037857009976</v>
       </c>
       <c r="C27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I27" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M27" t="n">
-        <v>486.8199999999999</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N27" t="n">
-        <v>725.41</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O27" t="n">
-        <v>964</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U27" t="n">
-        <v>735.7763817363891</v>
+        <v>562.4161926976942</v>
       </c>
       <c r="V27" t="n">
-        <v>500.6242735046464</v>
+        <v>327.2640844659515</v>
       </c>
       <c r="W27" t="n">
-        <v>257.1899300703029</v>
+        <v>327.2640844659515</v>
       </c>
       <c r="X27" t="n">
-        <v>49.33842986477009</v>
+        <v>327.2640844659515</v>
       </c>
       <c r="Y27" t="n">
-        <v>20.03413265278571</v>
+        <v>119.5037857009976</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C29" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D29" t="n">
-        <v>262.7143434343434</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E29" t="n">
-        <v>262.7143434343434</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="F29" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="G29" t="n">
-        <v>262.7143434343434</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2389935105428</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3148450952013</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723581055</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.1449945653449</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.3399447079929</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S29" t="n">
-        <v>964.0000000000439</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T29" t="n">
-        <v>738.6506570059718</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U29" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V29" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W29" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X29" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y29" t="n">
-        <v>262.7143434343434</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>145.0207557777026</v>
+        <v>145.0779112883388</v>
       </c>
       <c r="C30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I30" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="N30" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V30" t="n">
-        <v>728.8478917682573</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="W30" t="n">
-        <v>728.8478917682573</v>
+        <v>728.9050472788936</v>
       </c>
       <c r="X30" t="n">
-        <v>520.9963915627245</v>
+        <v>521.0535470733607</v>
       </c>
       <c r="Y30" t="n">
-        <v>313.2360927977706</v>
+        <v>313.2932483084068</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>19.28</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="C32" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="D32" t="n">
-        <v>19.28</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="E32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F32" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I32" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J32" t="n">
-        <v>19.27999999994063</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K32" t="n">
-        <v>122.2389935105719</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L32" t="n">
-        <v>302.3148450952305</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M32" t="n">
-        <v>519.2904723581346</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N32" t="n">
-        <v>725.144994565374</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O32" t="n">
-        <v>874.339944708022</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P32" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q32" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R32" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S32" t="n">
-        <v>964.000000000073</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T32" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U32" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V32" t="n">
-        <v>262.7143434343434</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W32" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X32" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y32" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>49.33842986477009</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I33" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J33" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K33" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L33" t="n">
-        <v>304.1765223866491</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M33" t="n">
-        <v>542.7665223866492</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N33" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O33" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R33" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="T33" t="n">
-        <v>964</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="U33" t="n">
-        <v>735.7763817363891</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="V33" t="n">
-        <v>500.6242735046464</v>
+        <v>790.6398109613051</v>
       </c>
       <c r="W33" t="n">
-        <v>257.1899300703029</v>
+        <v>547.1910343172051</v>
       </c>
       <c r="X33" t="n">
-        <v>49.33842986477009</v>
+        <v>339.3395341116723</v>
       </c>
       <c r="Y33" t="n">
-        <v>49.33842986477009</v>
+        <v>193.7341723913397</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="C34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="D34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="E34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="F34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="G34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="H34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="I34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="J34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="K34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="L34" t="n">
-        <v>46.59412500771298</v>
+        <v>856.8389900280785</v>
       </c>
       <c r="M34" t="n">
-        <v>85.78216319993516</v>
+        <v>896.0270282203006</v>
       </c>
       <c r="N34" t="n">
-        <v>129.4730138553714</v>
+        <v>939.7178788757369</v>
       </c>
       <c r="O34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R34" t="n">
-        <v>153.8122904902707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V34" t="n">
-        <v>19.28</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="X34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
       <c r="Y34" t="n">
-        <v>19.28</v>
+        <v>829.5248650203655</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C35" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D35" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E35" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F35" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I35" t="n">
-        <v>19.28</v>
+        <v>19.28114311021275</v>
       </c>
       <c r="J35" t="n">
-        <v>19.27999999994063</v>
+        <v>19.28114311021275</v>
       </c>
       <c r="K35" t="n">
-        <v>122.295005910863</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L35" t="n">
-        <v>302.3708574955216</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M35" t="n">
-        <v>519.3464847584257</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N35" t="n">
-        <v>725.2010069656651</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O35" t="n">
-        <v>874.3959571083132</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V35" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W35" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X35" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y35" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>420.1807237893668</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="C36" t="n">
-        <v>245.7276945082398</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="D36" t="n">
-        <v>178.5174550054555</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="E36" t="n">
-        <v>19.28</v>
+        <v>166.5698337361135</v>
       </c>
       <c r="F36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I36" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K36" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L36" t="n">
-        <v>19.28</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M36" t="n">
-        <v>234.7819638733197</v>
+        <v>487.8483949674443</v>
       </c>
       <c r="N36" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O36" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P36" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R36" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S36" t="n">
-        <v>790.5826554506689</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T36" t="n">
-        <v>588.3960608094349</v>
+        <v>806.4575656638924</v>
       </c>
       <c r="U36" t="n">
-        <v>588.3960608094349</v>
+        <v>578.2339474002815</v>
       </c>
       <c r="V36" t="n">
-        <v>588.3960608094349</v>
+        <v>578.2339474002815</v>
       </c>
       <c r="W36" t="n">
-        <v>588.3960608094349</v>
+        <v>334.7851707561815</v>
       </c>
       <c r="X36" t="n">
-        <v>588.3960608094349</v>
+        <v>334.7851707561815</v>
       </c>
       <c r="Y36" t="n">
-        <v>588.3960608094349</v>
+        <v>334.7851707561815</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K37" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L37" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M37" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N37" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q37" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="S37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y37" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="C38" t="n">
-        <v>710.4740411974295</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="D38" t="n">
-        <v>710.4740411974295</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="E38" t="n">
-        <v>467.0396977630861</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="F38" t="n">
-        <v>223.6053543287427</v>
+        <v>518.2486856454962</v>
       </c>
       <c r="G38" t="n">
-        <v>19.28</v>
+        <v>274.7999090013961</v>
       </c>
       <c r="H38" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="I38" t="n">
-        <v>19.28</v>
+        <v>31.35113235729608</v>
       </c>
       <c r="J38" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K38" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L38" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M38" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N38" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O38" t="n">
-        <v>874.3959571083725</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P38" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q38" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R38" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S38" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="U38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="V38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="W38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="X38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
       <c r="Y38" t="n">
-        <v>953.9083846317729</v>
+        <v>577.2332497330343</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>726.8405163024127</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="C39" t="n">
-        <v>726.8405163024127</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="D39" t="n">
-        <v>577.9061066411614</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="E39" t="n">
-        <v>418.6686516357059</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F39" t="n">
-        <v>272.1340936625909</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G39" t="n">
-        <v>133.4032682452064</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H39" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I39" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J39" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K39" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L39" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M39" t="n">
-        <v>374.6006659261865</v>
+        <v>417.4543050195419</v>
       </c>
       <c r="N39" t="n">
-        <v>473.3719638733197</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O39" t="n">
-        <v>711.9619638733197</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P39" t="n">
-        <v>894.6054414866707</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q39" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R39" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S39" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T39" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U39" t="n">
-        <v>862.8304705528857</v>
+        <v>914.2479596093278</v>
       </c>
       <c r="V39" t="n">
-        <v>862.8304705528857</v>
+        <v>679.0958513775852</v>
       </c>
       <c r="W39" t="n">
-        <v>862.8304705528857</v>
+        <v>435.6470747334852</v>
       </c>
       <c r="X39" t="n">
-        <v>862.8304705528857</v>
+        <v>227.7955745279523</v>
       </c>
       <c r="Y39" t="n">
-        <v>862.8304705528857</v>
+        <v>20.03527576299844</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L40" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M40" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N40" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S40" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T40" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y40" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C41" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D41" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E41" t="n">
-        <v>19.28</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J41" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K41" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L41" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M41" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N41" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O41" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P41" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q41" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R41" t="n">
-        <v>812.6170525846973</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S41" t="n">
-        <v>601.4856691642474</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="T41" t="n">
-        <v>376.1363261701753</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="U41" t="n">
-        <v>262.7143434343434</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="V41" t="n">
-        <v>19.28</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="W41" t="n">
-        <v>19.28</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="X41" t="n">
-        <v>19.28</v>
+        <v>559.1338160830064</v>
       </c>
       <c r="Y41" t="n">
-        <v>19.28</v>
+        <v>315.6850394389064</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>20.03413265278571</v>
+        <v>787.9255531013317</v>
       </c>
       <c r="C42" t="n">
-        <v>20.03413265278571</v>
+        <v>613.4725238202047</v>
       </c>
       <c r="D42" t="n">
-        <v>20.03413265278571</v>
+        <v>464.5381141589534</v>
       </c>
       <c r="E42" t="n">
-        <v>20.03413265278571</v>
+        <v>305.3006591534979</v>
       </c>
       <c r="F42" t="n">
-        <v>20.03413265278571</v>
+        <v>158.7661011803829</v>
       </c>
       <c r="G42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I42" t="n">
-        <v>20.03413265278571</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J42" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K42" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L42" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M42" t="n">
-        <v>473.3719638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="N42" t="n">
-        <v>711.9619638733197</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O42" t="n">
-        <v>711.9619638733197</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P42" t="n">
-        <v>894.6054414866707</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R42" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S42" t="n">
-        <v>964</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="T42" t="n">
-        <v>761.813405358766</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="U42" t="n">
-        <v>533.5897870951551</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="V42" t="n">
-        <v>298.4376788634124</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="W42" t="n">
-        <v>55.00333542906893</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="X42" t="n">
-        <v>55.00333542906893</v>
+        <v>956.1408901213997</v>
       </c>
       <c r="Y42" t="n">
-        <v>20.03413265278571</v>
+        <v>956.1408901213997</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L43" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M43" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N43" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P43" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q43" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="R43" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="S43" t="n">
-        <v>153.8122904902707</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="T43" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="U43" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="V43" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="W43" t="n">
-        <v>19.28</v>
+        <v>66.78106667958005</v>
       </c>
       <c r="X43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y43" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="44">
@@ -7607,76 +7607,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>559.0910937821268</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C44" t="n">
-        <v>559.0910937821268</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D44" t="n">
-        <v>315.6567503477834</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E44" t="n">
-        <v>72.22240691343993</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F44" t="n">
-        <v>72.22240691343993</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G44" t="n">
-        <v>72.22240691343993</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H44" t="n">
-        <v>72.22240691343993</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J44" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K44" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L44" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M44" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N44" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O44" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P44" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q44" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R44" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S44" t="n">
-        <v>802.5254372164702</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T44" t="n">
-        <v>802.5254372164702</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U44" t="n">
-        <v>802.5254372164702</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="V44" t="n">
-        <v>802.5254372164702</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W44" t="n">
-        <v>802.5254372164702</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X44" t="n">
-        <v>802.5254372164702</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y44" t="n">
-        <v>559.0910937821268</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="45">
@@ -7686,76 +7686,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>243.7921879279772</v>
+        <v>344.6327430815143</v>
       </c>
       <c r="C45" t="n">
-        <v>243.7921879279772</v>
+        <v>170.1797138003873</v>
       </c>
       <c r="D45" t="n">
-        <v>243.7921879279772</v>
+        <v>21.24530413913604</v>
       </c>
       <c r="E45" t="n">
-        <v>243.7921879279772</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="F45" t="n">
-        <v>243.7921879279772</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="G45" t="n">
-        <v>132.6491355924207</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="H45" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="I45" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J45" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K45" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L45" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M45" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N45" t="n">
-        <v>613.1906659261865</v>
+        <v>656.0584510084244</v>
       </c>
       <c r="O45" t="n">
-        <v>851.7806659261865</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="P45" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q45" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R45" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S45" t="n">
-        <v>689.4131260035546</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T45" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U45" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V45" t="n">
-        <v>487.2265313623206</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W45" t="n">
-        <v>243.7921879279772</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="X45" t="n">
-        <v>243.7921879279772</v>
+        <v>720.6083788665362</v>
       </c>
       <c r="Y45" t="n">
-        <v>243.7921879279772</v>
+        <v>512.8480801015824</v>
       </c>
     </row>
     <row r="46">
@@ -7765,76 +7765,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K46" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L46" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M46" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N46" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T46" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y46" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
   </sheetData>
@@ -7971,7 +7971,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O2" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P2" t="n">
         <v>321.7987081714826</v>
@@ -8038,25 +8038,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K3" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L3" t="n">
-        <v>356.2331311670658</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M3" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N3" t="n">
-        <v>372.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O3" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P3" t="n">
-        <v>318.4627686399372</v>
+        <v>238.6269471880057</v>
       </c>
       <c r="Q3" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R3" t="n">
         <v>45.52166981132082</v>
@@ -8196,7 +8196,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K5" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L5" t="n">
         <v>417.6612145504504</v>
@@ -8278,16 +8278,16 @@
         <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>368.526819785625</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O6" t="n">
-        <v>383.5962444444444</v>
+        <v>360.302996258564</v>
       </c>
       <c r="P6" t="n">
         <v>318.4627686399372</v>
@@ -8433,7 +8433,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L8" t="n">
         <v>417.6612145504504</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L9" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M9" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
-        <v>186.8300115967677</v>
+        <v>231.1529892133073</v>
       </c>
       <c r="O9" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P9" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q9" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8670,7 +8670,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L11" t="n">
         <v>417.6612145504504</v>
@@ -8755,16 +8755,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M12" t="n">
-        <v>383.1340339220183</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N12" t="n">
-        <v>244.694574784155</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q12" t="n">
         <v>139.9817740860215</v>
@@ -8919,7 +8919,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O14" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P14" t="n">
         <v>321.7987081714826</v>
@@ -8986,19 +8986,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>264.4652370125786</v>
+        <v>184.6294155606472</v>
       </c>
       <c r="L15" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9985353972331</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N15" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O15" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P15" t="n">
         <v>318.4627686399372</v>
@@ -9144,7 +9144,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L17" t="n">
         <v>417.6612145504504</v>
@@ -9223,19 +9223,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K18" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
-        <v>241.9030217474054</v>
+        <v>359.8407857361378</v>
       </c>
       <c r="N18" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O18" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P18" t="n">
         <v>318.4627686399372</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9466,19 +9466,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N21" t="n">
-        <v>301.2228591725469</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889778</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9700,22 +9700,22 @@
         <v>264.4652370125786</v>
       </c>
       <c r="L24" t="n">
-        <v>173.0976943544532</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>383.1340339220183</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N24" t="n">
-        <v>372.3417120833333</v>
+        <v>301.248502863135</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q24" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>45.52166981132082</v>
@@ -9861,7 +9861,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M26" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N26" t="n">
         <v>437.3469244119842</v>
@@ -9940,16 +9940,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M27" t="n">
-        <v>255.4868966228399</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N27" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
         <v>139.9817740860215</v>
@@ -10092,7 +10092,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K29" t="n">
-        <v>324.0888343889632</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L29" t="n">
         <v>417.6612145504504</v>
@@ -10180,10 +10180,10 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>301.2062135585481</v>
+        <v>301.248502863135</v>
       </c>
       <c r="O30" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P30" t="n">
         <v>318.4627686399372</v>
@@ -10329,7 +10329,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K32" t="n">
-        <v>324.0888343890525</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L32" t="n">
         <v>417.6612145504504</v>
@@ -10408,19 +10408,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>299.7048467786739</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M33" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N33" t="n">
-        <v>131.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O33" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
@@ -10581,7 +10581,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P35" t="n">
-        <v>321.7421299892966</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q35" t="n">
         <v>212.3149906599047</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>370.8403453034592</v>
       </c>
       <c r="M36" t="n">
-        <v>359.81278530921</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N36" t="n">
-        <v>372.3417120833333</v>
+        <v>186.8580120236956</v>
       </c>
       <c r="O36" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P36" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10818,7 +10818,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P38" t="n">
-        <v>321.7421299892367</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q38" t="n">
         <v>212.3149906599047</v>
@@ -10882,22 +10882,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L39" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>312.0431814381598</v>
       </c>
       <c r="N39" t="n">
-        <v>231.1106999087204</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O39" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P39" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>210.0772877358491</v>
@@ -11046,7 +11046,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11125,19 +11125,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M42" t="n">
-        <v>241.9030217474054</v>
+        <v>312.04082470182</v>
       </c>
       <c r="N42" t="n">
-        <v>372.3417120833333</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P42" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>45.52166981132082</v>
@@ -11280,7 +11280,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L44" t="n">
-        <v>417.6046363682045</v>
+        <v>417.6612145504504</v>
       </c>
       <c r="M44" t="n">
         <v>449.5135334928325</v>
@@ -11362,19 +11362,19 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M45" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N45" t="n">
-        <v>131.3417120833333</v>
+        <v>174.6270615612551</v>
       </c>
       <c r="O45" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P45" t="n">
-        <v>247.3272701151519</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R45" t="n">
         <v>45.52166981132082</v>
@@ -22555,25 +22555,25 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U2" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V2" t="n">
-        <v>327.7522584701349</v>
+        <v>125.4575720412377</v>
       </c>
       <c r="W2" t="n">
-        <v>349.240968717413</v>
+        <v>108.226679839754</v>
       </c>
       <c r="X2" t="n">
-        <v>358.5649190433906</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y2" t="n">
-        <v>145.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="3">
@@ -22586,7 +22586,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57065165286144</v>
+        <v>26.51519937644221</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -22680,7 +22680,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H4" t="n">
-        <v>162.2271725074396</v>
+        <v>115.2022481737659</v>
       </c>
       <c r="I4" t="n">
         <v>155.4504749272583</v>
@@ -22710,7 +22710,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>130.2684670434959</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S4" t="n">
         <v>224.0165980369723</v>
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C5" t="n">
         <v>365.2728917710076</v>
@@ -22750,22 +22750,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E5" t="n">
-        <v>381.9303700722618</v>
+        <v>380.1208739992256</v>
       </c>
       <c r="F5" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G5" t="n">
-        <v>184.4551164401535</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H5" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -22823,28 +22823,28 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7084989883157</v>
+        <v>27.26179070270013</v>
       </c>
       <c r="D6" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -22868,22 +22868,22 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W6" t="n">
-        <v>247.1698863426223</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X6" t="n">
         <v>205.7729852034775</v>
@@ -22914,7 +22914,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G7" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H7" t="n">
         <v>162.2271725074396</v>
@@ -22926,7 +22926,7 @@
         <v>93.35918011667277</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -22944,10 +22944,10 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R7" t="n">
-        <v>152.5379588693787</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S7" t="n">
         <v>224.0165980369723</v>
@@ -22987,19 +22987,19 @@
         <v>354.683041620683</v>
       </c>
       <c r="E8" t="n">
-        <v>380.1334596426677</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F8" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H8" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J8" t="n">
         <v>11.94928935461252</v>
@@ -23026,19 +23026,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R8" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V8" t="n">
-        <v>327.7522584701349</v>
+        <v>215.4233321629012</v>
       </c>
       <c r="W8" t="n">
         <v>349.240968717413</v>
@@ -23063,7 +23063,7 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E9" t="n">
         <v>157.6450804554009</v>
@@ -23075,13 +23075,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23114,10 +23114,10 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>197.051527993195</v>
       </c>
       <c r="V9" t="n">
-        <v>143.6665600725993</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>251.6949831609196</v>
@@ -23151,19 +23151,19 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H10" t="n">
         <v>162.2271725074396</v>
       </c>
       <c r="I10" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>93.35918011667277</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -23224,16 +23224,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E11" t="n">
-        <v>380.1334596426677</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F11" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G11" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H11" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23266,16 +23266,16 @@
         <v>149.8691179411497</v>
       </c>
       <c r="S11" t="n">
-        <v>209.0200695862453</v>
+        <v>189.2921341996816</v>
       </c>
       <c r="T11" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V11" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23294,16 +23294,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>145.0692123933839</v>
@@ -23342,28 +23342,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>86.36944326294565</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W12" t="n">
-        <v>247.1698863426223</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X12" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -23394,13 +23394,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I13" t="n">
-        <v>137.8921792844459</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -23418,7 +23418,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
-        <v>86.16204325169439</v>
+        <v>46.33425578299913</v>
       </c>
       <c r="R13" t="n">
         <v>177.2933913771695</v>
@@ -23461,16 +23461,16 @@
         <v>354.683041620683</v>
       </c>
       <c r="E14" t="n">
-        <v>381.9303700722618</v>
+        <v>380.1208739992256</v>
       </c>
       <c r="F14" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G14" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H14" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23497,7 +23497,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.193788784950724</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
         <v>149.8691179411497</v>
@@ -23534,25 +23534,25 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G15" t="n">
         <v>137.3435171632106</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -23582,19 +23582,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>61.6568969197465</v>
+        <v>137.0224969565572</v>
       </c>
       <c r="T15" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X15" t="n">
         <v>205.7729852034775</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G17" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H17" t="n">
-        <v>98.47480211576715</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I17" t="n">
-        <v>8.193788784950669</v>
+        <v>10.13979328157632</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23734,7 +23734,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R17" t="n">
         <v>149.8691179411497</v>
@@ -23768,19 +23768,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>145.0692123933839</v>
+        <v>66.07974793090087</v>
       </c>
       <c r="G18" t="n">
         <v>137.3435171632106</v>
@@ -23792,7 +23792,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23834,10 +23834,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X18" t="n">
-        <v>120.5147096390045</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23895,10 +23895,10 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>44.10642379180146</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T19" t="n">
         <v>227.9455894282815</v>
@@ -23926,13 +23926,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>113.6687527430239</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
@@ -23941,7 +23941,7 @@
         <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23983,19 +23983,19 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
-        <v>39.07285290783653</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V20" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
-        <v>128.731100678469</v>
+        <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>173.9525530126116</v>
       </c>
     </row>
     <row r="21">
@@ -24005,10 +24005,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>31.45815109468532</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -24017,10 +24017,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>60.50207587874962</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24071,10 +24071,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y21" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -24105,7 +24105,7 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I22" t="n">
-        <v>22.26350734189026</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J22" t="n">
         <v>93.35918011667277</v>
@@ -24150,7 +24150,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X22" t="n">
-        <v>225.7096553890372</v>
+        <v>92.52268780366916</v>
       </c>
       <c r="Y22" t="n">
         <v>218.5846533520948</v>
@@ -24163,7 +24163,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>382.7338416634806</v>
+        <v>182.3977453746509</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
@@ -24172,13 +24172,13 @@
         <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24187,7 +24187,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J23" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -24208,7 +24208,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
         <v>149.8691179411497</v>
@@ -24220,7 +24220,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>49.06355212232347</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24229,7 +24229,7 @@
         <v>349.240968717413</v>
       </c>
       <c r="X23" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y23" t="n">
         <v>386.2379386560536</v>
@@ -24245,13 +24245,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>147.4450655646388</v>
       </c>
       <c r="E24" t="n">
-        <v>157.6450804554009</v>
+        <v>48.24188835199618</v>
       </c>
       <c r="F24" t="n">
         <v>145.0692123933839</v>
@@ -24266,7 +24266,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24299,13 +24299,13 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
-        <v>175.924850211182</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W24" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -24339,7 +24339,7 @@
         <v>167.9909793584588</v>
       </c>
       <c r="H25" t="n">
-        <v>162.2271725074396</v>
+        <v>29.04020492207155</v>
       </c>
       <c r="I25" t="n">
         <v>155.4504749272583</v>
@@ -24378,7 +24378,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U25" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V25" t="n">
         <v>252.137643323828</v>
@@ -24400,7 +24400,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>141.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
         <v>365.2728917710076</v>
@@ -24409,10 +24409,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E26" t="n">
-        <v>381.9303700722618</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F26" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G26" t="n">
         <v>415.302737515135</v>
@@ -24448,19 +24448,19 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U26" t="n">
-        <v>171.0378204131177</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V26" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W26" t="n">
         <v>349.240968717413</v>
@@ -24469,7 +24469,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y26" t="n">
-        <v>386.2379386560536</v>
+        <v>173.9525530126115</v>
       </c>
     </row>
     <row r="27">
@@ -24482,7 +24482,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
-        <v>172.7084989883157</v>
+        <v>74.23467414969659</v>
       </c>
       <c r="D27" t="n">
         <v>147.4450655646388</v>
@@ -24530,7 +24530,7 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
@@ -24542,13 +24542,13 @@
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y27" t="n">
-        <v>176.6714415374398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -24637,7 +24637,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C29" t="n">
         <v>365.2728917710076</v>
@@ -24646,22 +24646,22 @@
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>381.9303700722618</v>
+        <v>181.5942737834322</v>
       </c>
       <c r="F29" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G29" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>339.4748021157671</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J29" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -24691,13 +24691,13 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U29" t="n">
-        <v>21.16870247192449</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V29" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W29" t="n">
         <v>349.240968717413</v>
@@ -24706,7 +24706,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y29" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="30">
@@ -24719,7 +24719,7 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>48.97174209464806</v>
+        <v>48.9162898182288</v>
       </c>
       <c r="D30" t="n">
         <v>147.4450655646388</v>
@@ -24798,7 +24798,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C31" t="n">
-        <v>34.05985351325981</v>
+        <v>167.2468210986278</v>
       </c>
       <c r="D31" t="n">
         <v>148.6154730182124</v>
@@ -24864,7 +24864,7 @@
         <v>225.7096553890372</v>
       </c>
       <c r="Y31" t="n">
-        <v>218.5846533520948</v>
+        <v>85.39768576672677</v>
       </c>
     </row>
     <row r="32">
@@ -24874,22 +24874,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C32" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D32" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>381.9303700722618</v>
+        <v>169.6449844288197</v>
       </c>
       <c r="F32" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G32" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H32" t="n">
         <v>339.4748021157671</v>
@@ -24898,7 +24898,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J32" t="n">
-        <v>11.94928935455374</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -24928,16 +24928,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>10.82304956405915</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
-        <v>10.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W32" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X32" t="n">
         <v>369.731100678469</v>
@@ -24956,7 +24956,7 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>143.6972447484512</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>147.4450655646388</v>
@@ -24977,7 +24977,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -25004,25 +25004,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W33" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>205.6826957773044</v>
+        <v>61.53338767417517</v>
       </c>
     </row>
     <row r="34">
@@ -25083,7 +25083,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T34" t="n">
         <v>227.9455894282815</v>
@@ -25095,7 +25095,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W34" t="n">
-        <v>286.522998336591</v>
+        <v>153.336030751223</v>
       </c>
       <c r="X34" t="n">
         <v>225.7096553890372</v>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C35" t="n">
-        <v>153.0000917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D35" t="n">
         <v>354.683041620683</v>
@@ -25123,10 +25123,10 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F35" t="n">
-        <v>165.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G35" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25135,7 +25135,7 @@
         <v>210.4758895704059</v>
       </c>
       <c r="J35" t="n">
-        <v>11.94928935455374</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -25174,13 +25174,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W35" t="n">
-        <v>349.240968717413</v>
+        <v>136.955583073971</v>
       </c>
       <c r="X35" t="n">
-        <v>369.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y35" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="36">
@@ -25193,16 +25193,16 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>80.9069284568823</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F36" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>137.3435171632106</v>
@@ -25214,7 +25214,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,19 +25241,19 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>44.14113474654525</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X36" t="n">
         <v>205.7729852034775</v>
@@ -25284,7 +25284,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G37" t="n">
-        <v>34.80401177309074</v>
+        <v>167.9909793584588</v>
       </c>
       <c r="H37" t="n">
         <v>162.2271725074396</v>
@@ -25317,7 +25317,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25351,28 +25351,28 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C38" t="n">
-        <v>124.2728917710076</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>165.8760457417114</v>
+        <v>348.4813272950487</v>
       </c>
       <c r="G38" t="n">
-        <v>213.0206367296798</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H38" t="n">
-        <v>339.4748021157671</v>
+        <v>98.46051323810809</v>
       </c>
       <c r="I38" t="n">
         <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -25396,13 +25396,13 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T38" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
         <v>251.3456529078365</v>
@@ -25427,25 +25427,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>31.90312894189904</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I39" t="n">
         <v>89.39663285141508</v>
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
         <v>171.6831711038378</v>
@@ -25484,19 +25484,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>225.9413820809748</v>
+        <v>176.6302781386795</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X39" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -25560,10 +25560,10 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T40" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U40" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V40" t="n">
         <v>252.137643323828</v>
@@ -25585,7 +25585,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>382.7338416634806</v>
+        <v>330.3082731757329</v>
       </c>
       <c r="C41" t="n">
         <v>365.2728917710076</v>
@@ -25597,7 +25597,7 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>406.8760457417114</v>
+        <v>165.8617568640524</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
@@ -25630,22 +25630,22 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>139.057889999363</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V41" t="n">
-        <v>86.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W41" t="n">
         <v>349.240968717413</v>
@@ -25654,7 +25654,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y41" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="42">
@@ -25664,22 +25664,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>112.2354442364965</v>
@@ -25715,25 +25715,25 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S42" t="n">
-        <v>171.6831711038378</v>
+        <v>163.8460683684937</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>10.69498316091961</v>
+        <v>251.6949831609196</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>171.063185028784</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25788,7 +25788,7 @@
         <v>2.721440735106512</v>
       </c>
       <c r="Q43" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>177.2933913771695</v>
@@ -25797,7 +25797,7 @@
         <v>224.0165980369723</v>
       </c>
       <c r="T43" t="n">
-        <v>94.75862184291347</v>
+        <v>227.9455894282815</v>
       </c>
       <c r="U43" t="n">
         <v>286.3190293564909</v>
@@ -25809,7 +25809,7 @@
         <v>286.522998336591</v>
       </c>
       <c r="X43" t="n">
-        <v>225.7096553890372</v>
+        <v>178.6847310553635</v>
       </c>
       <c r="Y43" t="n">
         <v>218.5846533520948</v>
@@ -25828,22 +25828,22 @@
         <v>365.2728917710076</v>
       </c>
       <c r="D44" t="n">
-        <v>113.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E44" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F44" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G44" t="n">
-        <v>415.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H44" t="n">
         <v>339.4748021157671</v>
       </c>
       <c r="I44" t="n">
-        <v>158.0629067261004</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J44" t="n">
         <v>11.94928935461252</v>
@@ -25867,22 +25867,22 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S44" t="n">
         <v>209.0200695862453</v>
       </c>
       <c r="T44" t="n">
-        <v>223.0958495641314</v>
+        <v>10.81046392068936</v>
       </c>
       <c r="U44" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V44" t="n">
-        <v>327.7522584701349</v>
+        <v>86.73796959247585</v>
       </c>
       <c r="W44" t="n">
         <v>349.240968717413</v>
@@ -25891,7 +25891,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y44" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="45">
@@ -25901,31 +25901,31 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>157.6450804554009</v>
+        <v>156.4471523630247</v>
       </c>
       <c r="F45" t="n">
         <v>145.0692123933839</v>
       </c>
       <c r="G45" t="n">
-        <v>27.31189535100974</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I45" t="n">
         <v>89.39663285141508</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -25949,13 +25949,13 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U45" t="n">
         <v>225.9413820809748</v>
@@ -25964,13 +25964,13 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W45" t="n">
-        <v>10.69498316091961</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X45" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y45" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -25983,7 +25983,7 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C46" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325981</v>
       </c>
       <c r="D46" t="n">
         <v>148.6154730182124</v>
@@ -26037,7 +26037,7 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U46" t="n">
-        <v>153.1320617711229</v>
+        <v>286.3190293564909</v>
       </c>
       <c r="V46" t="n">
         <v>252.137643323828</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>456932.5473417952</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>456932.5473418013</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>456932.5473417998</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>456932.5473418093</v>
+        <v>456941.8494611645</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>456932.5473418014</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>456932.5473417949</v>
+        <v>456941.8494611644</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>456932.547341795</v>
+        <v>456941.8494611643</v>
       </c>
     </row>
   </sheetData>
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="C2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="D2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="E2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="F2" t="n">
-        <v>124617.9674568532</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="G2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="H2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="I2" t="n">
-        <v>124617.9674568549</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="J2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="K2" t="n">
-        <v>124617.9674568544</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="L2" t="n">
-        <v>124617.9674568571</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="M2" t="n">
-        <v>124617.9674568549</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="N2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="O2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
       <c r="P2" t="n">
-        <v>124617.9674568531</v>
+        <v>124620.5043984993</v>
       </c>
     </row>
     <row r="3">
@@ -26313,7 +26313,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80764.643</v>
+        <v>80769.43153154773</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26337,7 +26337,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>63056.204</v>
+        <v>63059.94259910623</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="C4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="D4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="E4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="F4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="G4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966229</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966212</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="L4" t="n">
-        <v>179.5221438966319</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="M4" t="n">
-        <v>179.522143896623</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="N4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="O4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
       <c r="P4" t="n">
-        <v>179.5221438966159</v>
+        <v>179.5324977039669</v>
       </c>
     </row>
     <row r="5">
@@ -26417,49 +26417,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="C5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="D5" t="n">
-        <v>48280.39999999999</v>
+        <v>48281.26876376167</v>
       </c>
       <c r="E5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="F5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="G5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="M5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="N5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="O5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="P5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
     </row>
     <row r="6">
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-4606.597687043504</v>
+        <v>-4609.728394514095</v>
       </c>
       <c r="C6" t="n">
-        <v>76158.04531295653</v>
+        <v>76159.70313703365</v>
       </c>
       <c r="D6" t="n">
-        <v>76158.04531295656</v>
+        <v>76159.70313703368</v>
       </c>
       <c r="E6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="F6" t="n">
-        <v>109785.6453129566</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="G6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="H6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="I6" t="n">
-        <v>109785.6453129582</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="J6" t="n">
-        <v>46729.44131295649</v>
+        <v>46727.36053792744</v>
       </c>
       <c r="K6" t="n">
-        <v>109785.6453129578</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="L6" t="n">
-        <v>109785.6453129604</v>
+        <v>109787.3031370337</v>
       </c>
       <c r="M6" t="n">
-        <v>109785.6453129583</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="N6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="O6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
       <c r="P6" t="n">
-        <v>109785.6453129565</v>
+        <v>109787.3031370336</v>
       </c>
     </row>
   </sheetData>
@@ -26727,49 +26727,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="E4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="G4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="M4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
   </sheetData>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26898,43 +26898,43 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26944,19 +26944,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -26965,28 +26965,28 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27185,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34626,7 +34626,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O2" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P2" t="n">
         <v>90.5657124162131</v>
@@ -34693,25 +34693,25 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L3" t="n">
-        <v>217.6787513871916</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N3" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P3" t="n">
-        <v>184.4883612256069</v>
+        <v>104.6525397736754</v>
       </c>
       <c r="Q3" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -34851,7 +34851,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L5" t="n">
         <v>181.8947995804632</v>
@@ -34933,16 +34933,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>226.3927858636066</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O6" t="n">
-        <v>241</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="P6" t="n">
         <v>184.4883612256069</v>
@@ -35088,7 +35088,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L8" t="n">
         <v>181.8947995804632</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L9" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M9" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>55.48829951343436</v>
+        <v>99.81127712997396</v>
       </c>
       <c r="O9" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P9" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35325,7 +35325,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L11" t="n">
         <v>181.8947995804632</v>
@@ -35410,16 +35410,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M12" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N12" t="n">
-        <v>113.3528627008217</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -35574,7 +35574,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O14" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P14" t="n">
         <v>90.5657124162131</v>
@@ -35641,19 +35641,19 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>126.6237980382196</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="L15" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O15" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P15" t="n">
         <v>184.4883612256069</v>
@@ -35799,7 +35799,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L17" t="n">
         <v>181.8947995804632</v>
@@ -35878,19 +35878,19 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>99.76898782538704</v>
+        <v>217.7067518141195</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O18" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P18" t="n">
         <v>184.4883612256069</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36121,19 +36121,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N21" t="n">
-        <v>169.8811470892136</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439973</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36355,22 +36355,22 @@
         <v>126.6237980382196</v>
       </c>
       <c r="L24" t="n">
-        <v>34.54331457457899</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>241</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q24" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36516,7 +36516,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M26" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N26" t="n">
         <v>207.9338608153932</v>
@@ -36595,16 +36595,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M27" t="n">
-        <v>113.3528627008216</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N27" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36747,7 +36747,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>103.9989833439826</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L29" t="n">
         <v>181.8947995804632</v>
@@ -36835,10 +36835,10 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>169.8645014752148</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="O30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P30" t="n">
         <v>184.4883612256069</v>
@@ -36984,7 +36984,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>103.998983344072</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L32" t="n">
         <v>181.8947995804632</v>
@@ -37063,19 +37063,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>161.1504669987997</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O33" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
@@ -37236,7 +37236,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P35" t="n">
-        <v>90.50913423402712</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>232.285965523585</v>
       </c>
       <c r="M36" t="n">
-        <v>217.6787513871916</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N36" t="n">
-        <v>241</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="O36" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P36" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37473,7 +37473,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P38" t="n">
-        <v>90.50913423396717</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37537,22 +37537,22 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>169.9091475161415</v>
       </c>
       <c r="N39" t="n">
-        <v>99.76898782538704</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O39" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P39" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>70.09551364982758</v>
@@ -37701,7 +37701,7 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37780,19 +37780,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M42" t="n">
-        <v>99.76898782538704</v>
+        <v>169.9067907798017</v>
       </c>
       <c r="N42" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P42" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -37935,7 +37935,7 @@
         <v>104.0555615261842</v>
       </c>
       <c r="L44" t="n">
-        <v>181.8382213982173</v>
+        <v>181.8947995804632</v>
       </c>
       <c r="M44" t="n">
         <v>219.1673002655598</v>
@@ -38017,19 +38017,19 @@
         <v>232.285965523585</v>
       </c>
       <c r="M45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>43.28534947792182</v>
       </c>
       <c r="O45" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P45" t="n">
-        <v>113.3528627008217</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
